--- a/문서/weaponData.xlsx
+++ b/문서/weaponData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1011,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="9" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>

--- a/문서/weaponData.xlsx
+++ b/문서/weaponData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="520" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>idx</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>ㅇ</t>
+  </si>
+  <si>
+    <t>잿불가지</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="9" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
@@ -1045,10 +1048,27 @@
         <v>10</v>
       </c>
       <c r="D2" s="1">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
